--- a/artfynd/A 41254-2021 artfynd.xlsx
+++ b/artfynd/A 41254-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2111,6 +2111,1008 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131736077</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91848</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ol-Eskils-Stinarået Sydost, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>652016</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7030839</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131737048</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92127</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>658</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ol-Eskils-Stinarået Syd, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>652052</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7030971</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131737049</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92127</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>658</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ol-Eskils-Stinarået Syd, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>652033</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7030988</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131734573</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80325</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ol-Eskils-Stinarået Syd, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>652094</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7030938</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131736075</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91848</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ol-Eskils-Stinarået Sydost, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>652030</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7030867</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131737047</v>
+      </c>
+      <c r="B21" t="n">
+        <v>92127</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>658</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ol-Eskils-Stinarået Sydost, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>652018</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7030818</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131736922</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92288</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ol-Eskils-Stinarået Sydost, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>652031</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7030850</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131738060</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80365</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ol-Eskils-Stinarået Syd, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>652038</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7030886</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131739559</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91828</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ol-Eskils-Stinarået Sydost, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>652019</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7030821</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131739558</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91828</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ol-Eskils-Stinarået Syd, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>652037</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7030901</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Skorped</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristofer Wester</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41254-2021 artfynd.xlsx
+++ b/artfynd/A 41254-2021 artfynd.xlsx
@@ -2116,7 +2116,7 @@
         <v>131736077</v>
       </c>
       <c r="B16" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>131737048</v>
       </c>
       <c r="B17" t="n">
-        <v>92127</v>
+        <v>92128</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>131737049</v>
       </c>
       <c r="B18" t="n">
-        <v>92127</v>
+        <v>92128</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>131734573</v>
       </c>
       <c r="B19" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>131736075</v>
       </c>
       <c r="B20" t="n">
-        <v>91848</v>
+        <v>91849</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>131737047</v>
       </c>
       <c r="B21" t="n">
-        <v>92127</v>
+        <v>92128</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>131736922</v>
       </c>
       <c r="B22" t="n">
-        <v>92288</v>
+        <v>92289</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>131738060</v>
       </c>
       <c r="B23" t="n">
-        <v>80365</v>
+        <v>80366</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>131739559</v>
       </c>
       <c r="B24" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>131739558</v>
       </c>
       <c r="B25" t="n">
-        <v>91828</v>
+        <v>91829</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 41254-2021 artfynd.xlsx
+++ b/artfynd/A 41254-2021 artfynd.xlsx
@@ -2116,7 +2116,7 @@
         <v>131736077</v>
       </c>
       <c r="B16" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>131737048</v>
       </c>
       <c r="B17" t="n">
-        <v>92128</v>
+        <v>92131</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>131737049</v>
       </c>
       <c r="B18" t="n">
-        <v>92128</v>
+        <v>92131</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2412,45 +2412,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131734573</v>
+        <v>131736075</v>
       </c>
       <c r="B19" t="n">
-        <v>80326</v>
+        <v>91852</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ol-Eskils-Stinarået Syd, Ång</t>
+          <t>Ol-Eskils-Stinarået Sydost, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>652094</v>
+        <v>652030</v>
       </c>
       <c r="R19" t="n">
-        <v>7030938</v>
+        <v>7030867</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2513,41 +2509,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131736075</v>
+        <v>131734573</v>
       </c>
       <c r="B20" t="n">
-        <v>91849</v>
+        <v>80329</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ol-Eskils-Stinarået Sydost, Ång</t>
+          <t>Ol-Eskils-Stinarået Syd, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>652030</v>
+        <v>652094</v>
       </c>
       <c r="R20" t="n">
-        <v>7030867</v>
+        <v>7030938</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
         <v>131737047</v>
       </c>
       <c r="B21" t="n">
-        <v>92128</v>
+        <v>92131</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>131736922</v>
       </c>
       <c r="B22" t="n">
-        <v>92289</v>
+        <v>92292</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>131738060</v>
       </c>
       <c r="B23" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>131739559</v>
       </c>
       <c r="B24" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>131739558</v>
       </c>
       <c r="B25" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 41254-2021 artfynd.xlsx
+++ b/artfynd/A 41254-2021 artfynd.xlsx
@@ -2412,41 +2412,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131736075</v>
+        <v>131734573</v>
       </c>
       <c r="B19" t="n">
-        <v>91852</v>
+        <v>80329</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ol-Eskils-Stinarået Sydost, Ång</t>
+          <t>Ol-Eskils-Stinarået Syd, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>652030</v>
+        <v>652094</v>
       </c>
       <c r="R19" t="n">
-        <v>7030867</v>
+        <v>7030938</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2509,45 +2513,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131734573</v>
+        <v>131736075</v>
       </c>
       <c r="B20" t="n">
-        <v>80329</v>
+        <v>91852</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ol-Eskils-Stinarået Syd, Ång</t>
+          <t>Ol-Eskils-Stinarået Sydost, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>652094</v>
+        <v>652030</v>
       </c>
       <c r="R20" t="n">
-        <v>7030938</v>
+        <v>7030867</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2610,32 +2610,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131737047</v>
+        <v>131736922</v>
       </c>
       <c r="B21" t="n">
-        <v>92131</v>
+        <v>92292</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>652018</v>
+        <v>652031</v>
       </c>
       <c r="R21" t="n">
-        <v>7030818</v>
+        <v>7030850</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,32 +2711,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131736922</v>
+        <v>131737047</v>
       </c>
       <c r="B22" t="n">
-        <v>92292</v>
+        <v>92131</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>652031</v>
+        <v>652018</v>
       </c>
       <c r="R22" t="n">
-        <v>7030850</v>
+        <v>7030818</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 41254-2021 artfynd.xlsx
+++ b/artfynd/A 41254-2021 artfynd.xlsx
@@ -2412,45 +2412,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131734573</v>
+        <v>131736075</v>
       </c>
       <c r="B19" t="n">
-        <v>80329</v>
+        <v>91852</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ol-Eskils-Stinarået Syd, Ång</t>
+          <t>Ol-Eskils-Stinarået Sydost, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>652094</v>
+        <v>652030</v>
       </c>
       <c r="R19" t="n">
-        <v>7030938</v>
+        <v>7030867</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2513,41 +2509,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131736075</v>
+        <v>131734573</v>
       </c>
       <c r="B20" t="n">
-        <v>91852</v>
+        <v>80329</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ol-Eskils-Stinarået Sydost, Ång</t>
+          <t>Ol-Eskils-Stinarået Syd, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>652030</v>
+        <v>652094</v>
       </c>
       <c r="R20" t="n">
-        <v>7030867</v>
+        <v>7030938</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 41254-2021 artfynd.xlsx
+++ b/artfynd/A 41254-2021 artfynd.xlsx
@@ -2116,7 +2116,7 @@
         <v>131736077</v>
       </c>
       <c r="B16" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>131737048</v>
       </c>
       <c r="B17" t="n">
-        <v>92131</v>
+        <v>92137</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>131737049</v>
       </c>
       <c r="B18" t="n">
-        <v>92131</v>
+        <v>92137</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>131736075</v>
       </c>
       <c r="B19" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>131734573</v>
       </c>
       <c r="B20" t="n">
-        <v>80329</v>
+        <v>80331</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>131736922</v>
       </c>
       <c r="B21" t="n">
-        <v>92292</v>
+        <v>92298</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>131737047</v>
       </c>
       <c r="B22" t="n">
-        <v>92131</v>
+        <v>92137</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>131738060</v>
       </c>
       <c r="B23" t="n">
-        <v>80369</v>
+        <v>80371</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>131739559</v>
       </c>
       <c r="B24" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>131739558</v>
       </c>
       <c r="B25" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 41254-2021 artfynd.xlsx
+++ b/artfynd/A 41254-2021 artfynd.xlsx
@@ -2610,32 +2610,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131736922</v>
+        <v>131737047</v>
       </c>
       <c r="B21" t="n">
-        <v>92298</v>
+        <v>92137</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>652031</v>
+        <v>652018</v>
       </c>
       <c r="R21" t="n">
-        <v>7030850</v>
+        <v>7030818</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,32 +2711,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131737047</v>
+        <v>131736922</v>
       </c>
       <c r="B22" t="n">
-        <v>92137</v>
+        <v>92298</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>652018</v>
+        <v>652031</v>
       </c>
       <c r="R22" t="n">
-        <v>7030818</v>
+        <v>7030850</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 41254-2021 artfynd.xlsx
+++ b/artfynd/A 41254-2021 artfynd.xlsx
@@ -2610,32 +2610,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131737047</v>
+        <v>131736922</v>
       </c>
       <c r="B21" t="n">
-        <v>92137</v>
+        <v>92298</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>652018</v>
+        <v>652031</v>
       </c>
       <c r="R21" t="n">
-        <v>7030818</v>
+        <v>7030850</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,32 +2711,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131736922</v>
+        <v>131737047</v>
       </c>
       <c r="B22" t="n">
-        <v>92298</v>
+        <v>92137</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>652031</v>
+        <v>652018</v>
       </c>
       <c r="R22" t="n">
-        <v>7030850</v>
+        <v>7030818</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 41254-2021 artfynd.xlsx
+++ b/artfynd/A 41254-2021 artfynd.xlsx
@@ -2116,7 +2116,7 @@
         <v>131736077</v>
       </c>
       <c r="B16" t="n">
-        <v>91858</v>
+        <v>91861</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>131737048</v>
       </c>
       <c r="B17" t="n">
-        <v>92137</v>
+        <v>92140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>131737049</v>
       </c>
       <c r="B18" t="n">
-        <v>92137</v>
+        <v>92140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2412,41 +2412,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131736075</v>
+        <v>131734573</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>80334</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ol-Eskils-Stinarået Sydost, Ång</t>
+          <t>Ol-Eskils-Stinarået Syd, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>652030</v>
+        <v>652094</v>
       </c>
       <c r="R19" t="n">
-        <v>7030867</v>
+        <v>7030938</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2509,45 +2513,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131734573</v>
+        <v>131736075</v>
       </c>
       <c r="B20" t="n">
-        <v>80331</v>
+        <v>91861</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ol-Eskils-Stinarået Syd, Ång</t>
+          <t>Ol-Eskils-Stinarået Sydost, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>652094</v>
+        <v>652030</v>
       </c>
       <c r="R20" t="n">
-        <v>7030938</v>
+        <v>7030867</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2610,32 +2610,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131737047</v>
+        <v>131736922</v>
       </c>
       <c r="B21" t="n">
-        <v>92137</v>
+        <v>92301</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>652018</v>
+        <v>652031</v>
       </c>
       <c r="R21" t="n">
-        <v>7030818</v>
+        <v>7030850</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,32 +2711,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131736922</v>
+        <v>131737047</v>
       </c>
       <c r="B22" t="n">
-        <v>92298</v>
+        <v>92140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>652031</v>
+        <v>652018</v>
       </c>
       <c r="R22" t="n">
-        <v>7030850</v>
+        <v>7030818</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2815,7 +2815,7 @@
         <v>131738060</v>
       </c>
       <c r="B23" t="n">
-        <v>80371</v>
+        <v>80374</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>131739559</v>
       </c>
       <c r="B24" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>131739558</v>
       </c>
       <c r="B25" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 41254-2021 artfynd.xlsx
+++ b/artfynd/A 41254-2021 artfynd.xlsx
@@ -2116,7 +2116,7 @@
         <v>131736077</v>
       </c>
       <c r="B16" t="n">
-        <v>91861</v>
+        <v>91866</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>131737048</v>
       </c>
       <c r="B17" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>131737049</v>
       </c>
       <c r="B18" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2412,45 +2412,41 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131734573</v>
+        <v>131736075</v>
       </c>
       <c r="B19" t="n">
-        <v>80334</v>
+        <v>91866</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ol-Eskils-Stinarået Syd, Ång</t>
+          <t>Ol-Eskils-Stinarået Sydost, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>652094</v>
+        <v>652030</v>
       </c>
       <c r="R19" t="n">
-        <v>7030938</v>
+        <v>7030867</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2513,41 +2509,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131736075</v>
+        <v>131734573</v>
       </c>
       <c r="B20" t="n">
-        <v>91861</v>
+        <v>80339</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>229497</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ol-Eskils-Stinarået Sydost, Ång</t>
+          <t>Ol-Eskils-Stinarået Syd, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>652030</v>
+        <v>652094</v>
       </c>
       <c r="R20" t="n">
-        <v>7030867</v>
+        <v>7030938</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,7 +2613,7 @@
         <v>131736922</v>
       </c>
       <c r="B21" t="n">
-        <v>92301</v>
+        <v>92306</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>131737047</v>
       </c>
       <c r="B22" t="n">
-        <v>92140</v>
+        <v>92145</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>131738060</v>
       </c>
       <c r="B23" t="n">
-        <v>80374</v>
+        <v>80379</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>131739559</v>
       </c>
       <c r="B24" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>131739558</v>
       </c>
       <c r="B25" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 41254-2021 artfynd.xlsx
+++ b/artfynd/A 41254-2021 artfynd.xlsx
@@ -2116,7 +2116,7 @@
         <v>131736077</v>
       </c>
       <c r="B16" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>131737048</v>
       </c>
       <c r="B17" t="n">
-        <v>92145</v>
+        <v>92147</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>131737049</v>
       </c>
       <c r="B18" t="n">
-        <v>92145</v>
+        <v>92147</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>131736075</v>
       </c>
       <c r="B19" t="n">
-        <v>91866</v>
+        <v>91868</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>131734573</v>
       </c>
       <c r="B20" t="n">
-        <v>80339</v>
+        <v>80341</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2610,32 +2610,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131736922</v>
+        <v>131737047</v>
       </c>
       <c r="B21" t="n">
-        <v>92306</v>
+        <v>92147</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>652031</v>
+        <v>652018</v>
       </c>
       <c r="R21" t="n">
-        <v>7030850</v>
+        <v>7030818</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,32 +2711,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131737047</v>
+        <v>131736922</v>
       </c>
       <c r="B22" t="n">
-        <v>92145</v>
+        <v>92308</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>652018</v>
+        <v>652031</v>
       </c>
       <c r="R22" t="n">
-        <v>7030818</v>
+        <v>7030850</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2815,7 +2815,7 @@
         <v>131738060</v>
       </c>
       <c r="B23" t="n">
-        <v>80379</v>
+        <v>80381</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>131739559</v>
       </c>
       <c r="B24" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>131739558</v>
       </c>
       <c r="B25" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 41254-2021 artfynd.xlsx
+++ b/artfynd/A 41254-2021 artfynd.xlsx
@@ -2610,32 +2610,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131737047</v>
+        <v>131736922</v>
       </c>
       <c r="B21" t="n">
-        <v>92147</v>
+        <v>92308</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>652018</v>
+        <v>652031</v>
       </c>
       <c r="R21" t="n">
-        <v>7030818</v>
+        <v>7030850</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,32 +2711,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131736922</v>
+        <v>131737047</v>
       </c>
       <c r="B22" t="n">
-        <v>92308</v>
+        <v>92147</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>652031</v>
+        <v>652018</v>
       </c>
       <c r="R22" t="n">
-        <v>7030850</v>
+        <v>7030818</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 41254-2021 artfynd.xlsx
+++ b/artfynd/A 41254-2021 artfynd.xlsx
@@ -2610,32 +2610,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131736922</v>
+        <v>131737047</v>
       </c>
       <c r="B21" t="n">
-        <v>92308</v>
+        <v>92147</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>652031</v>
+        <v>652018</v>
       </c>
       <c r="R21" t="n">
-        <v>7030850</v>
+        <v>7030818</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,32 +2711,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131737047</v>
+        <v>131736922</v>
       </c>
       <c r="B22" t="n">
-        <v>92147</v>
+        <v>92308</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>652018</v>
+        <v>652031</v>
       </c>
       <c r="R22" t="n">
-        <v>7030818</v>
+        <v>7030850</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 41254-2021 artfynd.xlsx
+++ b/artfynd/A 41254-2021 artfynd.xlsx
@@ -2116,7 +2116,7 @@
         <v>131736077</v>
       </c>
       <c r="B16" t="n">
-        <v>91868</v>
+        <v>91904</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>131737048</v>
       </c>
       <c r="B17" t="n">
-        <v>92147</v>
+        <v>92183</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>131737049</v>
       </c>
       <c r="B18" t="n">
-        <v>92147</v>
+        <v>92183</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>131736075</v>
       </c>
       <c r="B19" t="n">
-        <v>91868</v>
+        <v>91904</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>131734573</v>
       </c>
       <c r="B20" t="n">
-        <v>80341</v>
+        <v>80375</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>131737047</v>
       </c>
       <c r="B21" t="n">
-        <v>92147</v>
+        <v>92183</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>131736922</v>
       </c>
       <c r="B22" t="n">
-        <v>92308</v>
+        <v>92344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>131738060</v>
       </c>
       <c r="B23" t="n">
-        <v>80381</v>
+        <v>80415</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>131739559</v>
       </c>
       <c r="B24" t="n">
-        <v>91848</v>
+        <v>91884</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>131739558</v>
       </c>
       <c r="B25" t="n">
-        <v>91848</v>
+        <v>91884</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 41254-2021 artfynd.xlsx
+++ b/artfynd/A 41254-2021 artfynd.xlsx
@@ -2116,7 +2116,7 @@
         <v>131736077</v>
       </c>
       <c r="B16" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>131737048</v>
       </c>
       <c r="B17" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>131737049</v>
       </c>
       <c r="B18" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>131736075</v>
       </c>
       <c r="B19" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
         <v>131734573</v>
       </c>
       <c r="B20" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2610,32 +2610,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131737047</v>
+        <v>131736922</v>
       </c>
       <c r="B21" t="n">
-        <v>92188</v>
+        <v>92352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>652018</v>
+        <v>652031</v>
       </c>
       <c r="R21" t="n">
-        <v>7030818</v>
+        <v>7030850</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2711,32 +2711,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131736922</v>
+        <v>131737047</v>
       </c>
       <c r="B22" t="n">
-        <v>92349</v>
+        <v>92191</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2746,10 +2746,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>652031</v>
+        <v>652018</v>
       </c>
       <c r="R22" t="n">
-        <v>7030850</v>
+        <v>7030818</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2815,7 +2815,7 @@
         <v>131738060</v>
       </c>
       <c r="B23" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>131739559</v>
       </c>
       <c r="B24" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>131739558</v>
       </c>
       <c r="B25" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 41254-2021 artfynd.xlsx
+++ b/artfynd/A 41254-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120679150</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120678396</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737047</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737048</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737049</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120678911</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,6 +1398,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120679388</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1460,6 +1500,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120679551</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1557,6 +1602,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120679666</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1654,6 +1704,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120679930</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1755,6 +1810,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739558</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1856,6 +1916,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131739559</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1953,6 +2018,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120678528</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2050,6 +2120,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120679171</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2147,6 +2222,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120679343</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2248,6 +2328,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131736922</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2345,6 +2430,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120678718</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2442,6 +2532,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120679957</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2543,6 +2638,11 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131738060</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2645,6 +2745,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120678254</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2747,6 +2852,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120689989</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2848,8 +2958,37 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131734573</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>